--- a/Eval1.xlsx
+++ b/Eval1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Evaluacion Asesores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4765011-E772-4FB1-BB50-5D3FBF7ACCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20133EAE-402B-44D9-89FC-E923FB4A893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9F464F4F-AE2E-4692-B991-6D68C8E444AE}"/>
   </bookViews>
@@ -194,9 +194,6 @@
     <t>Ofrece Marcas Isola, Alfonzo Rivas</t>
   </si>
   <si>
-    <t>Ofrece Marcas Alinieve, Incosa, Alesca</t>
-  </si>
-  <si>
     <t>Ofrece Marcas Miceven, Puig, Gaduca, Calven</t>
   </si>
   <si>
@@ -234,6 +231,9 @@
   </si>
   <si>
     <t>Link de Registro Fotografico</t>
+  </si>
+  <si>
+    <t>Ofrece Marcas Alinieve/Giomar, Incosa, Alesca</t>
   </si>
 </sst>
 </file>
@@ -626,39 +626,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -670,270 +646,292 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1651,711 +1649,729 @@
         <f ca="1">2:27</f>
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
     </row>
     <row r="3" spans="1:17" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="99"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10" t="s">
+      <c r="E4" s="105"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="13" t="s">
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="101"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="15" t="s">
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="13" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="103"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="19" t="s">
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="13" t="s">
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="19" t="s">
+      <c r="C8" s="96"/>
+      <c r="D8" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="22" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="K8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="13" t="s">
+      <c r="M8" s="3"/>
+      <c r="N8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25" t="s">
+      <c r="C9" s="58"/>
+      <c r="D9" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="27" t="str">
+      <c r="E9" s="48"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="66" t="str">
         <f>IFERROR(+AVERAGE(H9:L14),"")</f>
         <v/>
       </c>
-      <c r="H9" s="95"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="97"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="13" t="s">
+      <c r="H9" s="33"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="25" t="s">
+      <c r="B10" s="59"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="32" t="s">
+      <c r="E10" s="48"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="25" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="32"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="33" t="s">
+      <c r="B12" s="59"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="32"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="33" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="32"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:17" ht="41.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="33" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="97"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="38" t="s">
+      <c r="E14" s="88"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="39" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="40" t="s">
+    <row r="15" spans="1:17" s="15" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="101"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="36"/>
     </row>
     <row r="16" spans="1:17" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="33" t="s">
+      <c r="C16" s="58"/>
+      <c r="D16" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="27" t="str">
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="66" t="str">
         <f>+IFERROR(AVERAGE(H16:L22),"")</f>
         <v/>
       </c>
-      <c r="H16" s="95"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="102"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="37"/>
     </row>
     <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="25" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="102"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="37"/>
     </row>
     <row r="18" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="25" t="s">
+      <c r="B18" s="59"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="102"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="37"/>
     </row>
     <row r="19" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="25" t="s">
+      <c r="B19" s="59"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="102"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="37"/>
     </row>
     <row r="20" spans="2:14" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="45" t="s">
+      <c r="B20" s="59"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="103"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="38"/>
     </row>
     <row r="21" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="49" t="s">
+      <c r="B21" s="83"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="38" t="s">
+      <c r="E21" s="94"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="49" t="s">
+      <c r="B22" s="85"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="50"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="104"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="39"/>
     </row>
     <row r="23" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="56"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="105"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="40"/>
     </row>
     <row r="24" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="60"/>
-      <c r="D24" s="74" t="s">
+      <c r="C24" s="74"/>
+      <c r="D24" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="75"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="61" t="str">
+      <c r="E24" s="51"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="77" t="str">
         <f>+IFERROR(AVERAGE(H24:L27),"")</f>
         <v/>
       </c>
-      <c r="H24" s="85"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="105"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="40"/>
     </row>
     <row r="25" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="29"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="74" t="s">
+      <c r="B25" s="59"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="105"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="40"/>
     </row>
     <row r="26" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="29"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="74" t="s">
+      <c r="B26" s="59"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="105"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="40"/>
     </row>
     <row r="27" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="74" t="s">
+      <c r="B27" s="61"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="105"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="40"/>
     </row>
     <row r="28" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="67"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="106"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="41"/>
     </row>
     <row r="29" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25" t="s">
+      <c r="C29" s="58"/>
+      <c r="D29" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="27" t="str">
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="66" t="str">
         <f>+IFERROR(AVERAGE(H29:L32),"")</f>
         <v/>
       </c>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="38" t="s">
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="25" t="s">
+      <c r="B30" s="59"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="107"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="42"/>
     </row>
     <row r="31" spans="2:14" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="77" t="s">
+      <c r="B31" s="59"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="78"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="108"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="43"/>
     </row>
     <row r="32" spans="2:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="25" t="s">
+      <c r="B32" s="61"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="108"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="43"/>
     </row>
     <row r="33" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="67"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="59"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="108"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="43"/>
     </row>
     <row r="34" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="68" t="str">
+      <c r="C34" s="58"/>
+      <c r="D34" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="63" t="str">
         <f>+IFERROR(AVERAGE(H34:L37),"")</f>
         <v/>
       </c>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="108"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="43"/>
     </row>
     <row r="35" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="25" t="s">
+      <c r="B35" s="59"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="108"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="43"/>
     </row>
     <row r="36" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="25" t="s">
+      <c r="B36" s="59"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="43"/>
+    </row>
+    <row r="37" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="61"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="108"/>
-    </row>
-    <row r="37" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="35"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="109"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="44"/>
     </row>
     <row r="38" spans="2:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="98" t="str">
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="30" t="str">
         <f>+IFERROR(AVERAGE(G34,G29,G24,G16,G9),"")</f>
         <v/>
       </c>
-      <c r="H38" s="99"/>
-      <c r="I38" s="99"/>
-      <c r="J38" s="99"/>
-      <c r="K38" s="99"/>
-      <c r="L38" s="100"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="71"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="22"/>
     </row>
     <row r="39" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
     </row>
     <row r="40" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="M40" s="9"/>
-      <c r="N40" s="88"/>
-    </row>
-    <row r="41" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N41" s="87"/>
-    </row>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="N15:N20"/>
-    <mergeCell ref="N22:N28"/>
-    <mergeCell ref="N30:N37"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B4:C7"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G9:G14"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C14"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="B24:C27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:G27"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="E7:G7"/>
@@ -2364,6 +2380,19 @@
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="H9:L9"/>
     <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:C22"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:G22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="N15:N20"/>
+    <mergeCell ref="N22:N28"/>
+    <mergeCell ref="N30:N37"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B33:L33"/>
     <mergeCell ref="B34:C37"/>
     <mergeCell ref="D34:F34"/>
@@ -2375,39 +2404,6 @@
     <mergeCell ref="B29:C32"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="G29:G32"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B23:L23"/>
-    <mergeCell ref="B24:C27"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:G27"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:C22"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:G22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C14"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:G14"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B4:C7"/>
-    <mergeCell ref="E4:L4"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
@@ -2431,86 +2427,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="94" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="2" spans="1:4" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="90"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="3" spans="1:4" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="27"/>
     </row>
     <row r="4" spans="1:4" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="90"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="92"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="28"/>
     </row>
     <row r="6" spans="1:4" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="93"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="29"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="70"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="29"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="93"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="77" t="s">
+      <c r="B8" s="70"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="29"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="93"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="77" t="s">
+      <c r="B9" s="70"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="93"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="93"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/Eval1.xlsx
+++ b/Eval1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Evaluacion Asesores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20133EAE-402B-44D9-89FC-E923FB4A893B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C483A0EC-29D2-4F83-8EC5-5078DE669B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9F464F4F-AE2E-4692-B991-6D68C8E444AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9F464F4F-AE2E-4692-B991-6D68C8E444AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluacion" sheetId="1" r:id="rId1"/>
